--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:40</t>
+    <t xml:space="preserve">2026-09-09 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:59</t>
+    <t xml:space="preserve">2026-09-18 17:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
@@ -30,120 +30,120 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartagena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
     <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viña del Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alemana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Pascua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartagena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilpué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algarrobo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Tabo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:03</t>
+    <t xml:space="preserve">2026-09-27 21:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -573,13 +573,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>837</v>
+        <v>22380</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1033</v>
+        <v>19099</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>81.03</v>
+        <v>117.18</v>
       </c>
     </row>
     <row r="3">
@@ -587,13 +587,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>31389</v>
+        <v>15597</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36135</v>
+        <v>14338</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>86.87</v>
+        <v>108.78</v>
       </c>
     </row>
     <row r="4">
@@ -601,13 +601,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>322004</v>
+        <v>8219</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>361371</v>
+        <v>7633</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>89.11</v>
+        <v>107.68</v>
       </c>
     </row>
     <row r="5">
@@ -615,13 +615,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>126828</v>
+        <v>53344</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>139310</v>
+        <v>49931</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>91.04</v>
+        <v>106.84</v>
       </c>
     </row>
     <row r="6">
@@ -629,13 +629,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>14903</v>
+        <v>16041</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16367</v>
+        <v>15174</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>91.06</v>
+        <v>105.71</v>
       </c>
     </row>
     <row r="7">
@@ -643,13 +643,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>15053</v>
+        <v>21073</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>16482</v>
+        <v>20663</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>91.33</v>
+        <v>101.98</v>
       </c>
     </row>
     <row r="8">
@@ -657,13 +657,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>19155</v>
+        <v>8071</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>20643</v>
+        <v>7994</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>92.79</v>
+        <v>100.96</v>
       </c>
     </row>
     <row r="9">
@@ -671,13 +671,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>9814</v>
+        <v>17910</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10558</v>
+        <v>17742</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>92.95</v>
+        <v>100.95</v>
       </c>
     </row>
     <row r="10">
@@ -685,13 +685,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>293802</v>
+        <v>38022</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>315732</v>
+        <v>37739</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>93.05</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="11">
@@ -699,13 +699,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>23766</v>
+        <v>11926</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>25321</v>
+        <v>11934</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>93.86</v>
+        <v>99.93</v>
       </c>
     </row>
     <row r="12">
@@ -713,13 +713,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>18893</v>
+        <v>6176</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>20071</v>
+        <v>6201</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>94.13</v>
+        <v>99.6</v>
       </c>
     </row>
     <row r="13">
@@ -727,13 +727,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>14392</v>
+        <v>166046</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>15213</v>
+        <v>167085</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>94.6</v>
+        <v>99.38</v>
       </c>
     </row>
     <row r="14">
@@ -741,13 +741,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>27631</v>
+        <v>67658</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>29170</v>
+        <v>68093</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>94.72</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="15">
@@ -755,13 +755,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>93123</v>
+        <v>17501</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>97572</v>
+        <v>17645</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>95.44</v>
+        <v>99.18</v>
       </c>
     </row>
     <row r="16">
@@ -769,13 +769,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7986</v>
+        <v>23197</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8277</v>
+        <v>23490</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>96.48</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="17">
@@ -783,13 +783,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>18678</v>
+        <v>52908</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>19266</v>
+        <v>53591</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>96.95</v>
+        <v>98.73</v>
       </c>
     </row>
     <row r="18">
@@ -797,13 +797,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>10941</v>
+        <v>24950</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>11263</v>
+        <v>25357</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>97.14</v>
+        <v>98.39</v>
       </c>
     </row>
     <row r="19">
@@ -811,13 +811,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>81386</v>
+        <v>44895</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>83494</v>
+        <v>45889</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>97.48</v>
+        <v>97.83</v>
       </c>
     </row>
     <row r="20">
@@ -825,13 +825,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>25885</v>
+        <v>94461</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>26533</v>
+        <v>96761</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>97.56</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="21">
@@ -839,13 +839,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>94461</v>
+        <v>25885</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>96761</v>
+        <v>26533</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>97.62</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="22">
@@ -853,13 +853,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>44895</v>
+        <v>81386</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45889</v>
+        <v>83494</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>97.83</v>
+        <v>97.48</v>
       </c>
     </row>
     <row r="23">
@@ -867,13 +867,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>24950</v>
+        <v>10941</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>25357</v>
+        <v>11263</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>98.39</v>
+        <v>97.14</v>
       </c>
     </row>
     <row r="24">
@@ -881,13 +881,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>52908</v>
+        <v>18678</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>53591</v>
+        <v>19266</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>98.73</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="25">
@@ -895,13 +895,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>23197</v>
+        <v>7986</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>23490</v>
+        <v>8277</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>98.75</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="26">
@@ -909,13 +909,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>17501</v>
+        <v>93123</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>17645</v>
+        <v>97572</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>99.18</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="27">
@@ -923,13 +923,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>67658</v>
+        <v>27631</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>68093</v>
+        <v>29170</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>99.36</v>
+        <v>94.72</v>
       </c>
     </row>
     <row r="28">
@@ -937,13 +937,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>166046</v>
+        <v>14392</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>167085</v>
+        <v>15213</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>99.38</v>
+        <v>94.6</v>
       </c>
     </row>
     <row r="29">
@@ -951,13 +951,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>6176</v>
+        <v>18893</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6201</v>
+        <v>20071</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>99.6</v>
+        <v>94.13</v>
       </c>
     </row>
     <row r="30">
@@ -965,13 +965,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>11926</v>
+        <v>23766</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>11934</v>
+        <v>25321</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>99.93</v>
+        <v>93.86</v>
       </c>
     </row>
     <row r="31">
@@ -979,13 +979,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>38022</v>
+        <v>293802</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>37739</v>
+        <v>315732</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>100.75</v>
+        <v>93.05</v>
       </c>
     </row>
     <row r="32">
@@ -993,13 +993,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>17910</v>
+        <v>9814</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>17742</v>
+        <v>10558</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>100.95</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="33">
@@ -1007,13 +1007,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>8071</v>
+        <v>19155</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>7994</v>
+        <v>20643</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>100.96</v>
+        <v>92.79</v>
       </c>
     </row>
     <row r="34">
@@ -1021,13 +1021,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>21073</v>
+        <v>15053</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>20663</v>
+        <v>16482</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>101.98</v>
+        <v>91.33</v>
       </c>
     </row>
     <row r="35">
@@ -1035,13 +1035,13 @@
         <v>37</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>16041</v>
+        <v>14903</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>15174</v>
+        <v>16367</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>105.71</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="36">
@@ -1049,13 +1049,13 @@
         <v>38</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>53344</v>
+        <v>126828</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>49931</v>
+        <v>139310</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>106.84</v>
+        <v>91.04</v>
       </c>
     </row>
     <row r="37">
@@ -1063,13 +1063,13 @@
         <v>39</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>8219</v>
+        <v>322004</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>7633</v>
+        <v>361371</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>107.68</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="38">
@@ -1077,13 +1077,13 @@
         <v>40</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>15597</v>
+        <v>31389</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>14338</v>
+        <v>36135</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>108.78</v>
+        <v>86.87</v>
       </c>
     </row>
     <row r="39">
@@ -1091,13 +1091,13 @@
         <v>41</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>22380</v>
+        <v>837</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>19099</v>
+        <v>1033</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>117.18</v>
+        <v>81.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:47</t>
+    <t xml:space="preserve">2026-10-05 05:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
